--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_TURKEY_BEARDED.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_TURKEY_BEARDED.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.25" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -584,10 +585,15 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -637,7 +643,8 @@
       </c>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -683,7 +690,8 @@
       </c>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -733,7 +741,8 @@
       </c>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -783,7 +792,8 @@
       </c>
       <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -833,7 +843,8 @@
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -883,7 +894,8 @@
       </c>
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="6" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -933,7 +945,8 @@
       </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -979,7 +992,8 @@
       </c>
       <c r="J11" s="6" t="inlineStr"/>
       <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="6" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1025,7 +1039,8 @@
       </c>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1071,7 +1086,8 @@
       </c>
       <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1117,7 +1133,8 @@
       </c>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1163,7 +1180,8 @@
       </c>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1213,7 +1231,8 @@
       </c>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1263,7 +1282,8 @@
       </c>
       <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:L17"/>
